--- a/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/HAT/HAT+50T+50EP+optim_purn/params_vs_psnr_analysis/HAT_hutcn_hyperopt_study_3cols.xlsx
+++ b/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/HAT/HAT+50T+50EP+optim_purn/params_vs_psnr_analysis/HAT_hutcn_hyperopt_study_3cols.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,6 +441,11 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>FLOPs (G) @ 48x48</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>PSNR (dB)</t>
         </is>
       </c>
@@ -453,6 +458,9 @@
         <v>610502</v>
       </c>
       <c r="C2" t="n">
+        <v>1.38540622</v>
+      </c>
+      <c r="D2" t="n">
         <v>29.29343376159668</v>
       </c>
     </row>
@@ -464,6 +472,9 @@
         <v>1262318</v>
       </c>
       <c r="C3" t="n">
+        <v>3.0373947</v>
+      </c>
+      <c r="D3" t="n">
         <v>28.13686599731445</v>
       </c>
     </row>
@@ -475,6 +486,9 @@
         <v>1548332</v>
       </c>
       <c r="C4" t="n">
+        <v>3.531779072</v>
+      </c>
+      <c r="D4" t="n">
         <v>30.75124855041504</v>
       </c>
     </row>
@@ -486,6 +500,9 @@
         <v>1186866</v>
       </c>
       <c r="C5" t="n">
+        <v>2.559898544</v>
+      </c>
+      <c r="D5" t="n">
         <v>27.87908134460449</v>
       </c>
     </row>
@@ -497,6 +514,9 @@
         <v>355304</v>
       </c>
       <c r="C6" t="n">
+        <v>0.786504448</v>
+      </c>
+      <c r="D6" t="n">
         <v>27.0904655456543</v>
       </c>
     </row>
@@ -508,6 +528,9 @@
         <v>689606</v>
       </c>
       <c r="C7" t="n">
+        <v>1.770233388</v>
+      </c>
+      <c r="D7" t="n">
         <v>27.81993522644043</v>
       </c>
     </row>
@@ -519,6 +542,9 @@
         <v>1281480</v>
       </c>
       <c r="C8" t="n">
+        <v>2.75201536</v>
+      </c>
+      <c r="D8" t="n">
         <v>29.51193733215332</v>
       </c>
     </row>
@@ -530,6 +556,9 @@
         <v>474938</v>
       </c>
       <c r="C9" t="n">
+        <v>1.1127051</v>
+      </c>
+      <c r="D9" t="n">
         <v>24.86910552978516</v>
       </c>
     </row>
@@ -541,6 +570,9 @@
         <v>851568</v>
       </c>
       <c r="C10" t="n">
+        <v>1.876783948</v>
+      </c>
+      <c r="D10" t="n">
         <v>28.04503974914551</v>
       </c>
     </row>
@@ -552,6 +584,9 @@
         <v>621586</v>
       </c>
       <c r="C11" t="n">
+        <v>1.51314104</v>
+      </c>
+      <c r="D11" t="n">
         <v>30.49579048156738</v>
       </c>
     </row>
@@ -563,6 +598,9 @@
         <v>1542252</v>
       </c>
       <c r="C12" t="n">
+        <v>3.295849472</v>
+      </c>
+      <c r="D12" t="n">
         <v>30.62513656616211</v>
       </c>
     </row>
@@ -574,6 +612,9 @@
         <v>1542252</v>
       </c>
       <c r="C13" t="n">
+        <v>3.295849472</v>
+      </c>
+      <c r="D13" t="n">
         <v>30.60265655517578</v>
       </c>
     </row>
@@ -585,6 +626,9 @@
         <v>1189116</v>
       </c>
       <c r="C14" t="n">
+        <v>2.559898544</v>
+      </c>
+      <c r="D14" t="n">
         <v>30.58478202819824</v>
       </c>
     </row>
@@ -596,6 +640,9 @@
         <v>1542252</v>
       </c>
       <c r="C15" t="n">
+        <v>3.295849472</v>
+      </c>
+      <c r="D15" t="n">
         <v>30.65867881774902</v>
       </c>
     </row>
@@ -607,6 +654,9 @@
         <v>1246942</v>
       </c>
       <c r="C16" t="n">
+        <v>3.0373947</v>
+      </c>
+      <c r="D16" t="n">
         <v>30.74385108947754</v>
       </c>
     </row>
@@ -618,6 +668,9 @@
         <v>1091996</v>
       </c>
       <c r="C17" t="n">
+        <v>2.689432368</v>
+      </c>
+      <c r="D17" t="n">
         <v>30.82767944335938</v>
       </c>
     </row>
@@ -629,6 +682,9 @@
         <v>1091996</v>
       </c>
       <c r="C18" t="n">
+        <v>2.689432368</v>
+      </c>
+      <c r="D18" t="n">
         <v>30.77752532958984</v>
       </c>
     </row>
@@ -640,6 +696,9 @@
         <v>859456</v>
       </c>
       <c r="C19" t="n">
+        <v>2.055851712</v>
+      </c>
+      <c r="D19" t="n">
         <v>30.68361015319824</v>
       </c>
     </row>
@@ -651,6 +710,9 @@
         <v>1091996</v>
       </c>
       <c r="C20" t="n">
+        <v>2.689432368</v>
+      </c>
+      <c r="D20" t="n">
         <v>30.6967945098877</v>
       </c>
     </row>
@@ -662,6 +724,9 @@
         <v>1246942</v>
       </c>
       <c r="C21" t="n">
+        <v>3.0373947</v>
+      </c>
+      <c r="D21" t="n">
         <v>30.60173759460449</v>
       </c>
     </row>
@@ -673,6 +738,9 @@
         <v>1246942</v>
       </c>
       <c r="C22" t="n">
+        <v>3.0373947</v>
+      </c>
+      <c r="D22" t="n">
         <v>30.8084400177002</v>
       </c>
     </row>
@@ -684,6 +752,9 @@
         <v>1091996</v>
       </c>
       <c r="C23" t="n">
+        <v>2.689432368</v>
+      </c>
+      <c r="D23" t="n">
         <v>30.78609313964844</v>
       </c>
     </row>
@@ -695,6 +766,9 @@
         <v>1138124</v>
       </c>
       <c r="C24" t="n">
+        <v>2.689432368</v>
+      </c>
+      <c r="D24" t="n">
         <v>30.69006423950195</v>
       </c>
     </row>
@@ -706,6 +780,9 @@
         <v>613094</v>
       </c>
       <c r="C25" t="n">
+        <v>1.521655564</v>
+      </c>
+      <c r="D25" t="n">
         <v>30.66629028320312</v>
       </c>
     </row>
@@ -717,6 +794,9 @@
         <v>1091996</v>
       </c>
       <c r="C26" t="n">
+        <v>2.689432368</v>
+      </c>
+      <c r="D26" t="n">
         <v>30.72054595947266</v>
       </c>
     </row>
@@ -728,6 +808,9 @@
         <v>1091996</v>
       </c>
       <c r="C27" t="n">
+        <v>2.689432368</v>
+      </c>
+      <c r="D27" t="n">
         <v>30.72132339477539</v>
       </c>
     </row>
@@ -739,6 +822,9 @@
         <v>1110870</v>
       </c>
       <c r="C28" t="n">
+        <v>2.44184958</v>
+      </c>
+      <c r="D28" t="n">
         <v>30.71733055114746</v>
       </c>
     </row>
@@ -750,6 +836,9 @@
         <v>1548332</v>
       </c>
       <c r="C29" t="n">
+        <v>3.531779072</v>
+      </c>
+      <c r="D29" t="n">
         <v>30.86795272827148</v>
       </c>
     </row>
